--- a/Config/Datas/forge_recipe.xlsx
+++ b/Config/Datas/forge_recipe.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -107,7 +107,7 @@
     <t/>
   </si>
   <si>
-    <t>1</t>
+    <t>small_knife</t>
   </si>
   <si>
     <t>gold,5</t>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>解锁示例（需持有钥匙）</t>
-  </si>
-  <si>
-    <t>small_stone</t>
   </si>
   <si>
     <t>HasItem</t>
@@ -141,14 +138,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,148 +594,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1100,6 +1090,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
+    <col min="6" max="6" width="34.625" customWidth="1"/>
     <col min="8" max="8" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1265,7 +1256,7 @@
         <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -1274,10 +1265,10 @@
         <v>27</v>
       </c>
       <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
         <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>33</v>
       </c>
       <c r="K6">
         <v>3</v>

--- a/Config/Datas/forge_recipe.xlsx
+++ b/Config/Datas/forge_recipe.xlsx
@@ -1,299 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="forge_recipe" sheetId="1" r:id="rId1"/>
+    <sheet name="forge_recipe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>recipe_type</t>
-  </si>
-  <si>
-    <t>sort</t>
-  </si>
-  <si>
-    <t>display_name</t>
-  </si>
-  <si>
-    <t>result_item_id</t>
-  </si>
-  <si>
-    <t>icon_sprite</t>
-  </si>
-  <si>
-    <t>materials</t>
-  </si>
-  <si>
-    <t>unlock_mode</t>
-  </si>
-  <si>
-    <t>unlock_param</t>
-  </si>
-  <si>
-    <t>unlock_item_min_count</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>EForgeRecipeType</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(list#sep=|),ForgeMaterialCost</t>
-  </si>
-  <si>
-    <t>EForgeUnlockMode</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>item_id,count 用|分隔多条</t>
-  </si>
-  <si>
-    <t>任务id/全局开关名/道具或item|数</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>small_knife</t>
-  </si>
-  <si>
-    <t>gold,5</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Misc</t>
-  </si>
-  <si>
-    <t>解锁示例（需持有钥匙）</t>
-  </si>
-  <si>
-    <t>HasItem</t>
-  </si>
-  <si>
-    <t>1|3</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -594,153 +472,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -794,11 +672,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1085,197 +1026,711 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="6" max="6" width="34.625" customWidth="1"/>
-    <col min="8" max="8" width="18.375" customWidth="1"/>
+    <col width="34.625" customWidth="1" min="6" max="6"/>
+    <col width="18.375" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>recipe_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sort</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>result_item_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>icon_sprite</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unlock_mode</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unlock_param</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>unlock_item_min_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EForgeRecipeType</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),ForgeMaterialCost</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EForgeUnlockMode</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>item_id,count 用|分隔多条</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>任务id/全局开关名/道具或item|数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>small_knife</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>gold,5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>解锁示例（需持有钥匙）</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>small_knife</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gold,5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>HasItem</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1|3</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>101</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>橡木长餐桌</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>furn_oak_refectory_table</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mat_seasoned_plank,8|mat_iron_ingot,2|mat_polishing_wax,1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>102</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>胡桃木雕花椅</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>furn_walnut_carved_chair</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mat_hardwood_log,3|mat_linen_cloth,2|mat_hide_glue,1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>103</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>天鹅绒帷幔床</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>furn_velvet_canopy_bed</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>mat_seasoned_plank,10|mat_velvet,4|mat_silk_thread,2|mat_bronze_ingot,2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5">
-        <v>1001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5">
+    <row r="10">
+      <c r="B10" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>104</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>黄铜烛火吊灯</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>furn_brass_candle_chandelier</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mat_bronze_ingot,5|mat_lantern_wax,4|mat_conductive_copper_wire,2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6">
-        <v>1002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>105</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>彩绘玻璃魔灯</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>furn_stained_glass_lamp</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>mat_colored_glass,4|mat_arcane_copper_plate,2|mat_lamp_oil,2|mat_mana_shard,3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>106</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>大理石盥洗台</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>furn_marble_washstand</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>mat_marble,5|mat_copper_ingot,2|mat_glass_pane,1|mat_lime,2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>107</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>炼金药剂柜</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>furn_alchemist_cabinet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>mat_seasoned_plank,6|mat_alchemical_glass,3|mat_hide_glue,2|mat_bronze_ingot,2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>108</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>占星师书写桌</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>furn_astrologer_writing_desk</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>mat_hardwood_log,5|loot_brass_inkwell,1|mat_crystal_lens,1|mat_silver_ingot,1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>109</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>符刻藏书架</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>furn_runed_bookshelf</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mat_spiritwood,5|mat_runed_stone,2|loot_torn_page,6|mat_sealing_wax,2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>镏金折屏</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>furn_gilded_room_divider</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>mat_silk_bolt,3|mat_dyed_cloth,3|mat_silver_ingot,2|mat_polishing_wax,2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>111</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>月纹木梳妆台</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>furn_moonwood_vanity</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>mat_moonwood,4|mat_silver_ingot,2|mat_glass_pane,2|loot_chipped_gem,2</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>112</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>秘法壁炉</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>furn_arcane_hearth</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>mat_granite,6|mat_obsidian,3|mat_mana_crystal,2|mat_warding_wax,2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>